--- a/artfynd/A 29287-2024 artfynd.xlsx
+++ b/artfynd/A 29287-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119376753</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 29287-2024 artfynd.xlsx
+++ b/artfynd/A 29287-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119376753</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 29287-2024 artfynd.xlsx
+++ b/artfynd/A 29287-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2666,6 +2666,220 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129021326</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92803</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Öster Rutsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>462085</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6703415</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129021334</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92803</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Öster Rutsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>462147</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6703344</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29287-2024 artfynd.xlsx
+++ b/artfynd/A 29287-2024 artfynd.xlsx
@@ -2671,7 +2671,7 @@
         <v>129021326</v>
       </c>
       <c r="B20" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129021334</v>
       </c>
       <c r="B21" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29287-2024 artfynd.xlsx
+++ b/artfynd/A 29287-2024 artfynd.xlsx
@@ -2671,7 +2671,7 @@
         <v>129021326</v>
       </c>
       <c r="B20" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129021334</v>
       </c>
       <c r="B21" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29287-2024 artfynd.xlsx
+++ b/artfynd/A 29287-2024 artfynd.xlsx
@@ -2671,7 +2671,7 @@
         <v>129021326</v>
       </c>
       <c r="B20" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129021334</v>
       </c>
       <c r="B21" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29287-2024 artfynd.xlsx
+++ b/artfynd/A 29287-2024 artfynd.xlsx
@@ -2671,7 +2671,7 @@
         <v>129021326</v>
       </c>
       <c r="B20" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129021334</v>
       </c>
       <c r="B21" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29287-2024 artfynd.xlsx
+++ b/artfynd/A 29287-2024 artfynd.xlsx
@@ -2671,7 +2671,7 @@
         <v>129021326</v>
       </c>
       <c r="B20" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129021334</v>
       </c>
       <c r="B21" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29287-2024 artfynd.xlsx
+++ b/artfynd/A 29287-2024 artfynd.xlsx
@@ -2671,7 +2671,7 @@
         <v>129021326</v>
       </c>
       <c r="B20" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129021334</v>
       </c>
       <c r="B21" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29287-2024 artfynd.xlsx
+++ b/artfynd/A 29287-2024 artfynd.xlsx
@@ -2671,7 +2671,7 @@
         <v>129021326</v>
       </c>
       <c r="B20" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129021334</v>
       </c>
       <c r="B21" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29287-2024 artfynd.xlsx
+++ b/artfynd/A 29287-2024 artfynd.xlsx
@@ -2671,7 +2671,7 @@
         <v>129021326</v>
       </c>
       <c r="B20" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129021334</v>
       </c>
       <c r="B21" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29287-2024 artfynd.xlsx
+++ b/artfynd/A 29287-2024 artfynd.xlsx
@@ -2671,7 +2671,7 @@
         <v>129021326</v>
       </c>
       <c r="B20" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129021334</v>
       </c>
       <c r="B21" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29287-2024 artfynd.xlsx
+++ b/artfynd/A 29287-2024 artfynd.xlsx
@@ -2671,7 +2671,7 @@
         <v>129021326</v>
       </c>
       <c r="B20" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129021334</v>
       </c>
       <c r="B21" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29287-2024 artfynd.xlsx
+++ b/artfynd/A 29287-2024 artfynd.xlsx
@@ -2671,7 +2671,7 @@
         <v>129021326</v>
       </c>
       <c r="B20" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129021334</v>
       </c>
       <c r="B21" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29287-2024 artfynd.xlsx
+++ b/artfynd/A 29287-2024 artfynd.xlsx
@@ -2671,7 +2671,7 @@
         <v>129021326</v>
       </c>
       <c r="B20" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129021334</v>
       </c>
       <c r="B21" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
